--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.65385558832182</v>
+        <v>3.843751533102295</v>
       </c>
       <c r="D2" t="n">
-        <v>23.03823095672395</v>
+        <v>3.743712530467641</v>
       </c>
       <c r="E2" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F2" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.48096246554401</v>
+        <v>3.653156400650901</v>
       </c>
       <c r="D3" t="n">
-        <v>22.16017225080473</v>
+        <v>3.601027990755768</v>
       </c>
       <c r="E3" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F3" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.54281246526217</v>
+        <v>3.988207025605102</v>
       </c>
       <c r="D4" t="n">
-        <v>24.72690293473235</v>
+        <v>4.018121726894008</v>
       </c>
       <c r="E4" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F4" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.49818216603505</v>
+        <v>3.655954601980695</v>
       </c>
       <c r="D5" t="n">
-        <v>23.28503569758219</v>
+        <v>3.783818300857106</v>
       </c>
       <c r="E5" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F5" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.25813318979569</v>
+        <v>3.9419466433418</v>
       </c>
       <c r="D6" t="n">
-        <v>24.88105899069962</v>
+        <v>4.043172085988688</v>
       </c>
       <c r="E6" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F6" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.51595558248879</v>
+        <v>6.583842782154429</v>
       </c>
       <c r="D7" t="n">
-        <v>40.24499954386566</v>
+        <v>6.53981242587817</v>
       </c>
       <c r="E7" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F7" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.28091416446546</v>
+        <v>5.245648551725639</v>
       </c>
       <c r="D8" t="n">
-        <v>31.88709299525764</v>
+        <v>5.181652611729366</v>
       </c>
       <c r="E8" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F8" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.22642911053249</v>
+        <v>4.261794730461529</v>
       </c>
       <c r="D9" t="n">
-        <v>25.8111617254567</v>
+        <v>4.194313780386714</v>
       </c>
       <c r="E9" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F9" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.02441583082783</v>
+        <v>2.116467572509522</v>
       </c>
       <c r="D10" t="n">
-        <v>13.15086081357743</v>
+        <v>2.137014882206332</v>
       </c>
       <c r="E10" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F10" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.94674904338986</v>
+        <v>6.978846719550852</v>
       </c>
       <c r="D11" t="n">
-        <v>43.19541121737642</v>
+        <v>7.019254322823669</v>
       </c>
       <c r="E11" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F11" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.44758499474129</v>
+        <v>5.11023256164546</v>
       </c>
       <c r="D12" t="n">
-        <v>31.16620908280554</v>
+        <v>5.0645089759559</v>
       </c>
       <c r="E12" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F12" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.16768089136166</v>
+        <v>5.22724814484627</v>
       </c>
       <c r="D13" t="n">
-        <v>32.55119312326675</v>
+        <v>5.289568882530847</v>
       </c>
       <c r="E13" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F13" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.84451750386914</v>
+        <v>5.012234094378735</v>
       </c>
       <c r="D14" t="n">
-        <v>31.2203555972518</v>
+        <v>5.073307784553418</v>
       </c>
       <c r="E14" t="n">
-        <v>7.686510817337476</v>
+        <v>1.24905800781734</v>
       </c>
       <c r="F14" t="n">
-        <v>7.660559755627149</v>
+        <v>1.244840960289412</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
